--- a/data/trans_orig/Q4503_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4503_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119848</t>
+          <t>121518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161815</t>
+          <t>163064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40426</t>
+          <t>42380</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170170</t>
+          <t>170924</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221648</t>
+          <t>222294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120371</t>
+          <t>118113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161856</t>
+          <t>159415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43743</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72332</t>
+          <t>73640</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171004</t>
+          <t>170436</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>224310</t>
+          <t>222148</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>167938</t>
+          <t>166237</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>213120</t>
+          <t>211577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>159734</t>
+          <t>158536</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>204610</t>
+          <t>204320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>339963</t>
+          <t>340422</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>403779</t>
+          <t>405924</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44505</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73414</t>
+          <t>73389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85075</t>
+          <t>85908</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122166</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>139676</t>
+          <t>138560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187544</t>
+          <t>182691</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144013</t>
+          <t>143734</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185204</t>
+          <t>188119</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>269146</t>
+          <t>267390</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>318159</t>
+          <t>320084</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423098</t>
+          <t>423680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>493275</t>
+          <t>491508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163492</t>
+          <t>164620</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214940</t>
+          <t>216517</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68504</t>
+          <t>67503</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103191</t>
+          <t>104778</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244471</t>
+          <t>242752</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>305949</t>
+          <t>305960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131430</t>
+          <t>130776</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175924</t>
+          <t>176086</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78968</t>
+          <t>80878</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120332</t>
+          <t>120770</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>223150</t>
+          <t>222343</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282511</t>
+          <t>284626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,76%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>299456</t>
+          <t>298862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>364247</t>
+          <t>362381</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>246703</t>
+          <t>246215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>301576</t>
+          <t>301540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>563613</t>
+          <t>558577</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>645018</t>
+          <t>645893</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65740</t>
+          <t>64465</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99151</t>
+          <t>100294</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102518</t>
+          <t>103135</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146666</t>
+          <t>144982</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179036</t>
+          <t>179389</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236015</t>
+          <t>233775</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>182811</t>
+          <t>181199</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>238531</t>
+          <t>235052</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>356706</t>
+          <t>357607</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>417030</t>
+          <t>417727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>553221</t>
+          <t>554811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>638160</t>
+          <t>640235</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>109285</t>
+          <t>108624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>150705</t>
+          <t>155336</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99114</t>
+          <t>98054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139716</t>
+          <t>136778</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>219071</t>
+          <t>217342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276977</t>
+          <t>274159</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109394</t>
+          <t>108700</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151745</t>
+          <t>152471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62573</t>
+          <t>64088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95848</t>
+          <t>96741</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>181627</t>
+          <t>182019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236438</t>
+          <t>238431</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>166161</t>
+          <t>167456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>215071</t>
+          <t>213335</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117424</t>
+          <t>114559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157116</t>
+          <t>157070</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>295045</t>
+          <t>297118</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>356822</t>
+          <t>358522</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>47945</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81343</t>
+          <t>79514</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55937</t>
+          <t>56680</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86559</t>
+          <t>88509</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111273</t>
+          <t>110290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>152700</t>
+          <t>155428</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>145652</t>
+          <t>143886</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190324</t>
+          <t>190436</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258499</t>
+          <t>258882</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>307773</t>
+          <t>308477</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>408151</t>
+          <t>411249</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>479345</t>
+          <t>480108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,26%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149385</t>
+          <t>152042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199311</t>
+          <t>197302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106756</t>
+          <t>105114</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150074</t>
+          <t>148300</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>268876</t>
+          <t>267794</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>333088</t>
+          <t>332306</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>174009</t>
+          <t>173969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>224072</t>
+          <t>220343</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115904</t>
+          <t>113561</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>159448</t>
+          <t>157930</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>302938</t>
+          <t>300093</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>368421</t>
+          <t>363592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230354</t>
+          <t>230822</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>283805</t>
+          <t>282569</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>222162</t>
+          <t>220541</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>276321</t>
+          <t>277097</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>467804</t>
+          <t>466935</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>546284</t>
+          <t>543702</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91040</t>
+          <t>92173</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>128100</t>
+          <t>129786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112571</t>
+          <t>112780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>156506</t>
+          <t>155638</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>214960</t>
+          <t>214357</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271955</t>
+          <t>271278</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>180976</t>
+          <t>181450</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231106</t>
+          <t>232228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>363515</t>
+          <t>362156</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>423402</t>
+          <t>423242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>558457</t>
+          <t>559207</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>635947</t>
+          <t>640124</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>590150</t>
+          <t>587166</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>679792</t>
+          <t>678947</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>342352</t>
+          <t>345318</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>416815</t>
+          <t>422395</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>956130</t>
+          <t>958724</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1077521</t>
+          <t>1076422</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>572498</t>
+          <t>576535</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>664729</t>
+          <t>666059</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>335225</t>
+          <t>331692</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>409389</t>
+          <t>407869</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>930941</t>
+          <t>931155</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1041380</t>
+          <t>1046958</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>910774</t>
+          <t>916478</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1021040</t>
+          <t>1020974</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>791715</t>
+          <t>790991</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>891243</t>
+          <t>894595</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1733942</t>
+          <t>1726403</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1885133</t>
+          <t>1878397</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>277017</t>
+          <t>276381</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>345586</t>
+          <t>345664</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>390914</t>
+          <t>390174</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>467706</t>
+          <t>469805</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>685311</t>
+          <t>688680</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>790906</t>
+          <t>789107</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>695778</t>
+          <t>695882</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>792127</t>
+          <t>793791</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1299252</t>
+          <t>1294751</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1410337</t>
+          <t>1414433</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2033405</t>
+          <t>2024117</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2187074</t>
+          <t>2181251</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177671</t>
+          <t>176254</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>226402</t>
+          <t>224827</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74841</t>
+          <t>74565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113129</t>
+          <t>109392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>259784</t>
+          <t>259355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>322745</t>
+          <t>323461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117901</t>
+          <t>118658</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161277</t>
+          <t>163737</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106667</t>
+          <t>105002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148315</t>
+          <t>147859</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239318</t>
+          <t>235843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>298199</t>
+          <t>295198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100155</t>
+          <t>99375</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>140541</t>
+          <t>142770</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130077</t>
+          <t>131520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>172783</t>
+          <t>174718</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>241027</t>
+          <t>237597</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>303710</t>
+          <t>298996</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28322</t>
+          <t>27837</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52820</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36547</t>
+          <t>35590</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62839</t>
+          <t>63115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72043</t>
+          <t>69855</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108365</t>
+          <t>108080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181299</t>
+          <t>180431</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>228514</t>
+          <t>227648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252063</t>
+          <t>252176</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>308629</t>
+          <t>304761</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449350</t>
+          <t>449135</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>523975</t>
+          <t>517530</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>231817</t>
+          <t>231733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>289404</t>
+          <t>291425</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>127478</t>
+          <t>125498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174647</t>
+          <t>172453</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374696</t>
+          <t>371242</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>450238</t>
+          <t>451446</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159915</t>
+          <t>159139</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>212438</t>
+          <t>211897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>114154</t>
+          <t>111060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160367</t>
+          <t>155962</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>287135</t>
+          <t>284944</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>352955</t>
+          <t>354151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184263</t>
+          <t>184120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>235200</t>
+          <t>237387</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179516</t>
+          <t>179794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>229548</t>
+          <t>233868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>381849</t>
+          <t>377218</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>456563</t>
+          <t>452665</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>33184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61489</t>
+          <t>60938</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91391</t>
+          <t>90752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133199</t>
+          <t>133578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128694</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>179833</t>
+          <t>181190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283965</t>
+          <t>283283</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347118</t>
+          <t>347991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>396398</t>
+          <t>399070</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465779</t>
+          <t>464184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699784</t>
+          <t>694433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>788596</t>
+          <t>787449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120519</t>
+          <t>120029</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>165079</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82151</t>
+          <t>83122</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123762</t>
+          <t>124198</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>211562</t>
+          <t>216113</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276469</t>
+          <t>276638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108698</t>
+          <t>107399</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>151108</t>
+          <t>150728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77357</t>
+          <t>76956</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114914</t>
+          <t>115624</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194333</t>
+          <t>194293</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>253704</t>
+          <t>252113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122975</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167934</t>
+          <t>167077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>115629</t>
+          <t>117315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157646</t>
+          <t>160012</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>251512</t>
+          <t>250083</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>312322</t>
+          <t>312791</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>27325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52099</t>
+          <t>52857</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>36535</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64223</t>
+          <t>64060</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68158</t>
+          <t>69715</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>106547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276885</t>
+          <t>276718</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>334452</t>
+          <t>333221</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>359874</t>
+          <t>362816</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>418799</t>
+          <t>421131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,47%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>654164</t>
+          <t>656889</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>735866</t>
+          <t>738130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>226136</t>
+          <t>225810</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>279144</t>
+          <t>281652</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>184343</t>
+          <t>183787</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>236000</t>
+          <t>238987</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419765</t>
+          <t>422047</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>494647</t>
+          <t>498753</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>182058</t>
+          <t>186867</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>238136</t>
+          <t>236442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>143692</t>
+          <t>142547</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>191713</t>
+          <t>191469</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>343534</t>
+          <t>341649</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>417109</t>
+          <t>413735</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>189335</t>
+          <t>189154</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>242068</t>
+          <t>242105</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169310</t>
+          <t>167382</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>221428</t>
+          <t>219981</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>372015</t>
+          <t>371213</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>446054</t>
+          <t>444813</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44954</t>
+          <t>44779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>75359</t>
+          <t>74047</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>103766</t>
+          <t>104730</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148829</t>
+          <t>145890</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>158012</t>
+          <t>154346</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>208707</t>
+          <t>206079</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>188823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>241213</t>
+          <t>235248</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>326795</t>
+          <t>324995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>386715</t>
+          <t>389931</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>527383</t>
+          <t>529527</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>610965</t>
+          <t>611700</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>807651</t>
+          <t>802055</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>911033</t>
+          <t>912100</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>508853</t>
+          <t>508023</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>596047</t>
+          <t>595223</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1336545</t>
+          <t>1343174</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1473806</t>
+          <t>1474856</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>615554</t>
+          <t>613268</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>713756</t>
+          <t>711017</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>478495</t>
+          <t>484874</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>567045</t>
+          <t>567858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1121381</t>
+          <t>1120103</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1250439</t>
+          <t>1246488</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,9%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>639968</t>
+          <t>640580</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>737742</t>
+          <t>735491</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>640976</t>
+          <t>639808</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>738920</t>
+          <t>733555</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1305653</t>
+          <t>1308020</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1439694</t>
+          <t>1439094</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>153402</t>
+          <t>155699</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>209889</t>
+          <t>209435</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>294976</t>
+          <t>297220</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>368198</t>
+          <t>367527</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>468493</t>
+          <t>467127</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>558749</t>
+          <t>552968</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>973262</t>
+          <t>979684</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1090162</t>
+          <t>1085850</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1401723</t>
+          <t>1400631</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1520034</t>
+          <t>1516923</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2409099</t>
+          <t>2409499</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2565591</t>
+          <t>2575185</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la gorra o sombrero para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117401</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160052</t>
+          <t>158261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>63090</t>
+          <t>61426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94912</t>
+          <t>92571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188793</t>
+          <t>188431</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>240599</t>
+          <t>242651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130276</t>
+          <t>133427</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175043</t>
+          <t>175171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101662</t>
+          <t>103347</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141742</t>
+          <t>141634</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244495</t>
+          <t>244315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>302858</t>
+          <t>304818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111581</t>
+          <t>110678</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>154401</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>118166</t>
+          <t>117392</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160615</t>
+          <t>156963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>238433</t>
+          <t>238862</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>295752</t>
+          <t>298983</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50963</t>
+          <t>50137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81970</t>
+          <t>83287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44866</t>
+          <t>44745</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72817</t>
+          <t>72448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104741</t>
+          <t>104309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>148393</t>
+          <t>145798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165836</t>
+          <t>161981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>210358</t>
+          <t>209419</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>254859</t>
+          <t>255488</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305896</t>
+          <t>305355</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431529</t>
+          <t>429838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500693</t>
+          <t>500076</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140594</t>
+          <t>139840</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>187775</t>
+          <t>188048</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110426</t>
+          <t>110380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156672</t>
+          <t>154082</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260839</t>
+          <t>258393</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>327761</t>
+          <t>323079</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,71%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>260281</t>
+          <t>256758</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>319782</t>
+          <t>315110</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205842</t>
+          <t>205799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261710</t>
+          <t>258561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>480869</t>
+          <t>478943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559063</t>
+          <t>564291</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,43%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215934</t>
+          <t>214185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>268812</t>
+          <t>267908</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>226775</t>
+          <t>228492</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>284227</t>
+          <t>280985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>458863</t>
+          <t>457408</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>536328</t>
+          <t>534189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61604</t>
+          <t>62860</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95450</t>
+          <t>97622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78142</t>
+          <t>80415</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118485</t>
+          <t>118319</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149530</t>
+          <t>150946</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>199143</t>
+          <t>202429</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>219317</t>
+          <t>220008</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>275859</t>
+          <t>275896</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,7 +9165,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296350</t>
+          <t>297021</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361230</t>
+          <t>361962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>535290</t>
+          <t>531673</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>619251</t>
+          <t>618161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87308</t>
+          <t>85948</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127650</t>
+          <t>127870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72129</t>
+          <t>71256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108199</t>
+          <t>108844</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>167028</t>
+          <t>166237</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221394</t>
+          <t>222277</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>213060</t>
+          <t>216045</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>264376</t>
+          <t>267054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234760</t>
+          <t>234490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>286714</t>
+          <t>287201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>461492</t>
+          <t>465860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>538866</t>
+          <t>540589</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193685</t>
+          <t>195276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>246474</t>
+          <t>249777</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>163316</t>
+          <t>162332</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212590</t>
+          <t>210115</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370946</t>
+          <t>371412</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>445394</t>
+          <t>443818</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21469</t>
+          <t>21640</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44789</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32551</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59141</t>
+          <t>56939</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>59488</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95039</t>
+          <t>94383</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136356</t>
+          <t>134763</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179841</t>
+          <t>179938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>177830</t>
+          <t>178227</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227008</t>
+          <t>227590</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>326700</t>
+          <t>325879</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>392455</t>
+          <t>393885</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139468</t>
+          <t>139601</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185404</t>
+          <t>187440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>124910</t>
+          <t>123749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171522</t>
+          <t>170635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>273055</t>
+          <t>271659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339534</t>
+          <t>339743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210306</t>
+          <t>210588</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>266221</t>
+          <t>262591</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>185722</t>
+          <t>186367</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>242329</t>
+          <t>239393</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>414687</t>
+          <t>413020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>493075</t>
+          <t>489479</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,74%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176184</t>
+          <t>176017</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>226282</t>
+          <t>225982</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>167156</t>
+          <t>169655</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219914</t>
+          <t>217721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>359133</t>
+          <t>358796</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>430060</t>
+          <t>427967</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,63%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>65187</t>
+          <t>64801</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>98990</t>
+          <t>99743</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88087</t>
+          <t>85105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>127447</t>
+          <t>126236</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159972</t>
+          <t>159428</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211108</t>
+          <t>212710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>230647</t>
+          <t>232598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>285698</t>
+          <t>288010</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>348001</t>
+          <t>352503</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>415255</t>
+          <t>414192</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>596214</t>
+          <t>601041</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>686045</t>
+          <t>681648</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,46%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>521210</t>
+          <t>522458</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>611335</t>
+          <t>612157</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>403021</t>
+          <t>401114</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>482573</t>
+          <t>481441</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>945529</t>
+          <t>949196</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1066318</t>
+          <t>1066299</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>862532</t>
+          <t>866566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>966830</t>
+          <t>973459</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>777572</t>
+          <t>776945</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>876102</t>
+          <t>877448</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1671082</t>
+          <t>1667964</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1816090</t>
+          <t>1816035</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,7 +10942,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>743993</t>
+          <t>748581</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>847968</t>
+          <t>841783</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>723126</t>
+          <t>720640</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>825266</t>
+          <t>820901</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1496245</t>
+          <t>1501162</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1641341</t>
+          <t>1637415</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,69%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>224735</t>
+          <t>223853</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>289124</t>
+          <t>288994</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>273181</t>
+          <t>272953</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>341456</t>
+          <t>340235</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>514100</t>
+          <t>512768</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>608839</t>
+          <t>608487</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>797902</t>
+          <t>799512</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>897703</t>
+          <t>904017</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1130886</t>
+          <t>1137991</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1250781</t>
+          <t>1253309</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1957193</t>
+          <t>1963260</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2116821</t>
+          <t>2117375</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4503_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4503_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121518</t>
+          <t>120665</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163064</t>
+          <t>163525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42380</t>
+          <t>41468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>69412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170924</t>
+          <t>168377</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>222294</t>
+          <t>222977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,15%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118113</t>
+          <t>118090</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>159415</t>
+          <t>160218</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>42854</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>73640</t>
+          <t>74355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170436</t>
+          <t>168163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>222148</t>
+          <t>219231</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>166237</t>
+          <t>166350</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>211577</t>
+          <t>214858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158536</t>
+          <t>159797</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>204320</t>
+          <t>204793</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>340422</t>
+          <t>339980</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>405924</t>
+          <t>406013</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45988</t>
+          <t>44494</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73389</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85908</t>
+          <t>85011</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122879</t>
+          <t>122807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>138560</t>
+          <t>140007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>182691</t>
+          <t>183793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143734</t>
+          <t>142894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188119</t>
+          <t>187113</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>267390</t>
+          <t>266618</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>320084</t>
+          <t>319601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>423680</t>
+          <t>423250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>491508</t>
+          <t>492862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164620</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>216517</t>
+          <t>216365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67503</t>
+          <t>66907</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104778</t>
+          <t>103390</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>242752</t>
+          <t>244766</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>305960</t>
+          <t>310752</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130776</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>176086</t>
+          <t>179889</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80878</t>
+          <t>80261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120770</t>
+          <t>118921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>222343</t>
+          <t>223593</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>284626</t>
+          <t>285687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>298862</t>
+          <t>299509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>362381</t>
+          <t>360209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>246215</t>
+          <t>242498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>301540</t>
+          <t>302259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>558577</t>
+          <t>561966</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>645893</t>
+          <t>643440</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64465</t>
+          <t>64017</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100294</t>
+          <t>100550</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103135</t>
+          <t>102467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144982</t>
+          <t>145162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>179389</t>
+          <t>176255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233775</t>
+          <t>232826</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,08%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>181199</t>
+          <t>183421</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235052</t>
+          <t>242278</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>357607</t>
+          <t>357874</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>417727</t>
+          <t>419106</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554811</t>
+          <t>551303</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>640235</t>
+          <t>635232</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>108624</t>
+          <t>111727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>155336</t>
+          <t>153718</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98054</t>
+          <t>98560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>136778</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>217342</t>
+          <t>215196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>274159</t>
+          <t>278226</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108700</t>
+          <t>109802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>152471</t>
+          <t>152423</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64088</t>
+          <t>62460</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96741</t>
+          <t>96945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>182019</t>
+          <t>184145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238431</t>
+          <t>235922</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,33%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>167456</t>
+          <t>166546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>213335</t>
+          <t>214412</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114559</t>
+          <t>116327</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157070</t>
+          <t>158600</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>297118</t>
+          <t>296942</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>358522</t>
+          <t>359136</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47945</t>
+          <t>48466</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79514</t>
+          <t>77684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56680</t>
+          <t>56508</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>88509</t>
+          <t>86601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>110290</t>
+          <t>110385</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>155428</t>
+          <t>155268</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>143886</t>
+          <t>144240</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>190436</t>
+          <t>190302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>258882</t>
+          <t>256775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>308477</t>
+          <t>310882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>411249</t>
+          <t>413391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>480108</t>
+          <t>486003</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>152042</t>
+          <t>150049</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197302</t>
+          <t>198762</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>105114</t>
+          <t>106359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148300</t>
+          <t>148231</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>267794</t>
+          <t>266165</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>332306</t>
+          <t>334911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>173969</t>
+          <t>172891</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220343</t>
+          <t>222300</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>113561</t>
+          <t>114136</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>157930</t>
+          <t>158040</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>300093</t>
+          <t>302319</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>363592</t>
+          <t>365737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>230822</t>
+          <t>227680</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282569</t>
+          <t>280756</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>220541</t>
+          <t>222227</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>277097</t>
+          <t>278714</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>466935</t>
+          <t>469293</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>543702</t>
+          <t>542890</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,44%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92173</t>
+          <t>90544</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>129786</t>
+          <t>129443</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>112780</t>
+          <t>111572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>155638</t>
+          <t>155056</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>214357</t>
+          <t>212515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271278</t>
+          <t>269777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>181450</t>
+          <t>180680</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>232228</t>
+          <t>232738</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>362156</t>
+          <t>362106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>423242</t>
+          <t>423467</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>559207</t>
+          <t>559202</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>640124</t>
+          <t>645668</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>587166</t>
+          <t>588684</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>678947</t>
+          <t>675709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>345318</t>
+          <t>346624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>422395</t>
+          <t>417455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>958724</t>
+          <t>956166</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1076422</t>
+          <t>1075938</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>576535</t>
+          <t>573835</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>666059</t>
+          <t>668001</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>331692</t>
+          <t>331289</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>407869</t>
+          <t>407646</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>931155</t>
+          <t>933224</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1046958</t>
+          <t>1048667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>916478</t>
+          <t>914554</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1020974</t>
+          <t>1013970</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>790991</t>
+          <t>790445</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>894595</t>
+          <t>890238</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1726403</t>
+          <t>1737556</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1878397</t>
+          <t>1878170</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>276381</t>
+          <t>278118</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>345664</t>
+          <t>349244</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>390174</t>
+          <t>391435</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>469805</t>
+          <t>470762</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>688680</t>
+          <t>687227</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>789107</t>
+          <t>790801</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>695882</t>
+          <t>702031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>793791</t>
+          <t>794746</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1294751</t>
+          <t>1291248</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1414433</t>
+          <t>1416183</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2024117</t>
+          <t>2026825</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2181251</t>
+          <t>2178731</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>176254</t>
+          <t>177211</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224827</t>
+          <t>224766</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74565</t>
+          <t>71167</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>110863</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>259355</t>
+          <t>261785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>323461</t>
+          <t>323451</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118658</t>
+          <t>118080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163737</t>
+          <t>161424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105002</t>
+          <t>106657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>147859</t>
+          <t>151523</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>235843</t>
+          <t>235339</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>295198</t>
+          <t>297510</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>99375</t>
+          <t>101310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>142770</t>
+          <t>140121</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>131520</t>
+          <t>129176</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>174718</t>
+          <t>174545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>237597</t>
+          <t>244447</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298996</t>
+          <t>304540</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>27584</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>52536</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35590</t>
+          <t>36366</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>63115</t>
+          <t>64957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69855</t>
+          <t>70985</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108080</t>
+          <t>107068</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180431</t>
+          <t>180613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227648</t>
+          <t>229612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>252176</t>
+          <t>252356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>304761</t>
+          <t>304983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>449135</t>
+          <t>448993</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>517530</t>
+          <t>519946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>231733</t>
+          <t>233589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>291425</t>
+          <t>292316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125498</t>
+          <t>128508</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172453</t>
+          <t>174655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>371242</t>
+          <t>372886</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>451446</t>
+          <t>449448</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159139</t>
+          <t>162696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211897</t>
+          <t>211562</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>111060</t>
+          <t>114213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155962</t>
+          <t>158442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284944</t>
+          <t>286648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354151</t>
+          <t>354555</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184120</t>
+          <t>183126</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>237387</t>
+          <t>236857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>179794</t>
+          <t>178478</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>233868</t>
+          <t>233127</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>377218</t>
+          <t>377030</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>452665</t>
+          <t>449812</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33184</t>
+          <t>32122</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60938</t>
+          <t>61648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>90752</t>
+          <t>91857</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133578</t>
+          <t>135173</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131952</t>
+          <t>133467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181190</t>
+          <t>184711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283283</t>
+          <t>283973</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347991</t>
+          <t>344775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>399070</t>
+          <t>397552</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>464184</t>
+          <t>461485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694433</t>
+          <t>701166</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>787449</t>
+          <t>786620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>120029</t>
+          <t>120202</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>165079</t>
+          <t>165417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83122</t>
+          <t>81950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>124198</t>
+          <t>123023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216113</t>
+          <t>214259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>276638</t>
+          <t>275078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107399</t>
+          <t>106341</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>150728</t>
+          <t>148568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76956</t>
+          <t>77304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115624</t>
+          <t>116063</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>194293</t>
+          <t>196641</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>252113</t>
+          <t>254209</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,6%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>123548</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>167077</t>
+          <t>167139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>117315</t>
+          <t>116057</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>160012</t>
+          <t>158547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>250083</t>
+          <t>252970</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>312791</t>
+          <t>317557</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27325</t>
+          <t>27565</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52857</t>
+          <t>54174</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36535</t>
+          <t>35618</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64060</t>
+          <t>63092</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69715</t>
+          <t>67745</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>106547</t>
+          <t>105522</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>276718</t>
+          <t>275417</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333221</t>
+          <t>330194</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>362816</t>
+          <t>363542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>421131</t>
+          <t>420356</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,85%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>656889</t>
+          <t>654574</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>738130</t>
+          <t>740070</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225810</t>
+          <t>226295</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>281652</t>
+          <t>281868</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183787</t>
+          <t>180346</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>238987</t>
+          <t>235165</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>422047</t>
+          <t>424939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>498753</t>
+          <t>500372</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186867</t>
+          <t>185144</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>236442</t>
+          <t>238924</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>142547</t>
+          <t>143987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>191469</t>
+          <t>194353</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>341649</t>
+          <t>342486</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>413735</t>
+          <t>414632</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,8%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>189154</t>
+          <t>189539</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>242105</t>
+          <t>242938</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>167382</t>
+          <t>170856</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>219981</t>
+          <t>220170</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>371213</t>
+          <t>374605</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>444813</t>
+          <t>452164</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44779</t>
+          <t>44281</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74047</t>
+          <t>75450</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104730</t>
+          <t>102550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>145890</t>
+          <t>145861</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154346</t>
+          <t>156171</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>206079</t>
+          <t>208623</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>188823</t>
+          <t>186877</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>235248</t>
+          <t>239118</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>324995</t>
+          <t>323727</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>389931</t>
+          <t>387366</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>529527</t>
+          <t>527707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>611700</t>
+          <t>609461</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>802055</t>
+          <t>803329</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>912100</t>
+          <t>910094</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>508023</t>
+          <t>505539</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>595223</t>
+          <t>596064</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1343174</t>
+          <t>1336366</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1474856</t>
+          <t>1470835</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>613268</t>
+          <t>613211</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>711017</t>
+          <t>708913</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>484874</t>
+          <t>482272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>567858</t>
+          <t>566093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1120103</t>
+          <t>1118236</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1246488</t>
+          <t>1248461</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>640580</t>
+          <t>639450</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>735491</t>
+          <t>735283</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>639808</t>
+          <t>636263</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>733555</t>
+          <t>735886</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1308020</t>
+          <t>1308427</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1439094</t>
+          <t>1438990</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>155699</t>
+          <t>156898</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>209435</t>
+          <t>212665</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>297220</t>
+          <t>297709</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>367527</t>
+          <t>364186</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>467127</t>
+          <t>463759</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>552968</t>
+          <t>552030</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>979684</t>
+          <t>974113</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1085850</t>
+          <t>1088309</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1400631</t>
+          <t>1398120</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1516923</t>
+          <t>1519094</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2409499</t>
+          <t>2401461</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2575185</t>
+          <t>2574582</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>119016</t>
+          <t>118742</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158261</t>
+          <t>159865</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>61964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92571</t>
+          <t>94753</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>188431</t>
+          <t>189926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>242651</t>
+          <t>243054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133427</t>
+          <t>131534</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175171</t>
+          <t>174746</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103347</t>
+          <t>103288</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>141634</t>
+          <t>140543</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>244315</t>
+          <t>244304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>304818</t>
+          <t>303275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110678</t>
+          <t>109622</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>153202</t>
+          <t>151577</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>117392</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>156963</t>
+          <t>157531</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>238862</t>
+          <t>238940</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>298983</t>
+          <t>299503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50137</t>
+          <t>51841</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>83287</t>
+          <t>83625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44745</t>
+          <t>43876</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72448</t>
+          <t>72649</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104309</t>
+          <t>102560</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>145798</t>
+          <t>146146</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161981</t>
+          <t>161968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209419</t>
+          <t>210472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>255488</t>
+          <t>253082</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>305355</t>
+          <t>303948</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>429838</t>
+          <t>429106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>500076</t>
+          <t>503109</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,19%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139840</t>
+          <t>138611</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188048</t>
+          <t>186454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110380</t>
+          <t>109488</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154082</t>
+          <t>153410</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>258393</t>
+          <t>258828</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>323079</t>
+          <t>324670</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>256758</t>
+          <t>257744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315110</t>
+          <t>318235</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205799</t>
+          <t>204703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258561</t>
+          <t>258622</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>478943</t>
+          <t>480457</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564291</t>
+          <t>557879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,12%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>214185</t>
+          <t>215016</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>267908</t>
+          <t>270696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>228492</t>
+          <t>227732</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>280985</t>
+          <t>285600</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>457408</t>
+          <t>462476</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>534189</t>
+          <t>540983</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62860</t>
+          <t>61738</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97622</t>
+          <t>95161</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>80415</t>
+          <t>78459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118319</t>
+          <t>117760</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150946</t>
+          <t>150740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202429</t>
+          <t>202298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>220008</t>
+          <t>216643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>275896</t>
+          <t>275574</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297021</t>
+          <t>296028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>361962</t>
+          <t>360059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>531673</t>
+          <t>532599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>618161</t>
+          <t>614273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85948</t>
+          <t>85769</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127870</t>
+          <t>127295</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71256</t>
+          <t>70184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108844</t>
+          <t>106791</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166237</t>
+          <t>171242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>222277</t>
+          <t>220952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>216045</t>
+          <t>212121</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>267054</t>
+          <t>268176</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>234490</t>
+          <t>235186</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>287201</t>
+          <t>289386</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>465860</t>
+          <t>461584</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>540589</t>
+          <t>536132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>195276</t>
+          <t>195177</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>249777</t>
+          <t>245783</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>162332</t>
+          <t>164171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>210115</t>
+          <t>212327</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>371412</t>
+          <t>369597</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>443818</t>
+          <t>443141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,9%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21640</t>
+          <t>21298</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44789</t>
+          <t>45031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>31710</t>
+          <t>33476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56939</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59488</t>
+          <t>60533</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94383</t>
+          <t>94591</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>134763</t>
+          <t>135376</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>179938</t>
+          <t>180627</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178227</t>
+          <t>177000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>227590</t>
+          <t>227949</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>325879</t>
+          <t>327678</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>393885</t>
+          <t>395213</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139601</t>
+          <t>137352</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187440</t>
+          <t>186762</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123749</t>
+          <t>123176</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>170635</t>
+          <t>170368</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>271659</t>
+          <t>275945</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339743</t>
+          <t>339597</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>210588</t>
+          <t>209911</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262591</t>
+          <t>265223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>186367</t>
+          <t>188584</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>239393</t>
+          <t>239389</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>413020</t>
+          <t>410374</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>489479</t>
+          <t>487516</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176017</t>
+          <t>175820</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>225982</t>
+          <t>227814</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>169655</t>
+          <t>169320</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>217721</t>
+          <t>222056</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>358796</t>
+          <t>361215</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>427967</t>
+          <t>434943</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64801</t>
+          <t>64563</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>99743</t>
+          <t>98011</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85105</t>
+          <t>85618</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126236</t>
+          <t>124282</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>159428</t>
+          <t>162303</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>212710</t>
+          <t>216367</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>232598</t>
+          <t>230803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>288010</t>
+          <t>286733</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>352503</t>
+          <t>351268</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>414192</t>
+          <t>417752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>601041</t>
+          <t>594626</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>681648</t>
+          <t>681341</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,44%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>522458</t>
+          <t>522189</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>612157</t>
+          <t>612099</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,7 +10759,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>401114</t>
+          <t>400652</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>481441</t>
+          <t>479159</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>949196</t>
+          <t>945198</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1066299</t>
+          <t>1064766</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>866566</t>
+          <t>861622</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>973459</t>
+          <t>968289</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>776945</t>
+          <t>779389</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>877448</t>
+          <t>882202</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1667964</t>
+          <t>1666846</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1816035</t>
+          <t>1815194</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>748581</t>
+          <t>743308</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>841783</t>
+          <t>844836</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>720640</t>
+          <t>728308</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>820901</t>
+          <t>823453</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1501162</t>
+          <t>1491219</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1637415</t>
+          <t>1634486</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,64%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>223853</t>
+          <t>227610</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>288994</t>
+          <t>289893</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>272953</t>
+          <t>271373</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>340235</t>
+          <t>339299</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>512768</t>
+          <t>510000</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>608487</t>
+          <t>604416</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>799512</t>
+          <t>793275</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>904017</t>
+          <t>897834</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1137991</t>
+          <t>1134040</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1253309</t>
+          <t>1246669</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1963260</t>
+          <t>1963828</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2117375</t>
+          <t>2115836</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,61%</t>
         </is>
       </c>
     </row>
